--- a/DateBase/orders/Nha Thu_2026-7-20.xlsx
+++ b/DateBase/orders/Nha Thu_2026-7-20.xlsx
@@ -1255,6 +1255,9 @@
       <c r="G2" t="str">
         <v>01324755593109558551020606055551851253558355555551015315121055105102010520202015510555335555105102017510101081010151051515333015</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
